--- a/partner_results/ncit/ClassMissingGermanDefinition_ncit.xlsx
+++ b/partner_results/ncit/ClassMissingGermanDefinition_ncit.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>measurement device [ncit]</t>
+          <t>Raman spectroscopy [ncit]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Any device used to determine the dimension of an object.</t>
+          <t>Emission of electromagnetic energy with a shorter frequency (longer wavelength) than that of the incident monochromatic light. Arises from the low probability absorption of quanta with a higher energy than that required for a transition: the difference in energy is emitted as a lower frequency (energy) photon. Allows analysis of vibrational and rotational energy levels using visible incident light. [ NCI ]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pixel [ncit]</t>
+          <t>plasticizer [ncit]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The smallest resolvable rectangular area of an image, either on a screen or stored in memory.</t>
+          <t>A substance added to plastics or other materials to make or keep them soft or pliable.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,18 +484,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>activator [ncit]</t>
+          <t>measurement device [ncit]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vulcanizing system [dik]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A class of substances that binds to, activates and increases the activity of a target.</t>
+          <t>Any device used to determine the dimension of an object.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,18 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mechanical mixer [ncit]</t>
+          <t>monomer [ncit]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A mechanical component designed to blend materials.</t>
+          <t>A chemical subunit that can undergo polymerization by bonding to other subunits.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -522,18 +522,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>natural rubber [ncit]</t>
+          <t>standard deviation [ncit]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The natural extract of tropical rubber plants.</t>
+          <t>A measure of the range of values in a set of numbers. Standard deviation is a statistic used as a measure of the dispersion or variation in a distribution, equal to the square root of the arithmetic mean of the squares of the deviations from the arithmetic mean. (ncit defined)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -541,18 +541,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zinc [ncit]</t>
+          <t>colorimetry [ncit]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>An element with atomic symbol Zn, atomic number 30, and atomic weight 65.39.</t>
+          <t>An assessment used to quantify and describe the colors within the visible spectrum of light.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -560,18 +560,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>agent [ncit]</t>
+          <t>shape [ncit]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>An active power or cause (as principle, substance, physical or biological factor, etc.) that produces a specific effect.</t>
+          <t>The spatial arrangement of something as distinct from its substance.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -579,18 +579,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>peak [ncit]</t>
+          <t>activator [ncit]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>vulcanizing system [dik]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The most extreme possible amount or value; the highest point.</t>
+          <t>A class of substances that binds to, activates and increases the activity of a target.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -598,18 +598,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raman spectroscopy [ncit]</t>
+          <t>function [ncit]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Emission of electromagnetic energy with a shorter frequency (longer wavelength) than that of the incident monochromatic light. Arises from the low probability absorption of quanta with a higher energy than that required for a transition: the difference in energy is emitted as a lower frequency (energy) photon. Allows analysis of vibrational and rotational energy levels using visible incident light. [ NCI ]</t>
+          <t>The normal action performed by a structure or device.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -617,18 +617,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mass density [ncit]</t>
+          <t>validation [ncit]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A measure of the compactness of a substance, expressed as its mass per unit volume.</t>
+          <t>The act of validating; finding or testing the truth of something.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -636,18 +636,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>crosslink [ncit]</t>
+          <t>photometry [ncit]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>group [chebi]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Any covalent linkage between two polymers or between two different regions of the same polymer.</t>
+          <t>Measurement of the properties of light, especially luminous intensity.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -655,18 +655,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mixing [ncit]</t>
+          <t>supervisor [ncit]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To bring or combine together or with something else; add as an additional element or part.</t>
+          <t>An individual who is responsible for managing or operating a business, organization, team or department.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -674,18 +674,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mixer device [ncit]</t>
+          <t>crosslink [ncit]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>group [chebi]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A mechanical device designed to blend materials or an electronic device designed to blend signals.</t>
+          <t>Any covalent linkage between two polymers or between two different regions of the same polymer.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -693,18 +693,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>standard deviation [ncit]</t>
+          <t>agent [ncit]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A measure of the range of values in a set of numbers. Standard deviation is a statistic used as a measure of the dispersion or variation in a distribution, equal to the square root of the arithmetic mean of the squares of the deviations from the arithmetic mean. (ncit defined)</t>
+          <t>An active power or cause (as principle, substance, physical or biological factor, etc.) that produces a specific effect.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -712,18 +712,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>supervisor [ncit]</t>
+          <t>pixel [ncit]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>An individual who is responsible for managing or operating a business, organization, team or department.</t>
+          <t>The smallest resolvable rectangular area of an image, either on a screen or stored in memory.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -731,18 +731,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>validation [ncit]</t>
+          <t>group [ncit]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>chemical entity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The act of validating; finding or testing the truth of something.</t>
+          <t>Any number of entities (members) considered as a unit.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -750,18 +750,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>monomer [ncit]</t>
+          <t>mechanical mixer [ncit]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A chemical subunit that can undergo polymerization by bonding to other subunits.</t>
+          <t>A mechanical component designed to blend materials.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -769,18 +769,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>stearic acid [ncit]</t>
+          <t>correlation [ncit]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pure substance</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A saturated long-chain fatty acid with an 18-carbon backbone. Stearic acid is found in various animal and plant fats, and is a major component of cocoa butter and shea butter.</t>
+          <t>The degree to which two or more quantities or events are associated, a statistical relation between two or more variables such that systematic changes in the value of one variable are accompanied by systematic changes in the others. The collelation can be described by mathematical functions  (often a linear function is used). It’s a common tool for describing simple relationships without making a statement about cause and effect.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -788,18 +788,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>count [ncit]</t>
+          <t>correlation [ncit]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Determining the number or amount of something.</t>
+          <t>The degree to which two or more quantities or events are associated, a statistical relation between two or more variables such that systematic changes in the value of one variable are accompanied by systematic changes in the others. The collelation can be described by mathematical functions  (often a linear function is used). It’s a common tool for describing simple relationships without making a statement about cause and effect.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -807,18 +807,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>operator [ncit]</t>
+          <t>unit of mass density [ncit]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>measurement unit label</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A person that operates some apparatus or machine.</t>
+          <t>An indication of the type of unit of measure being used to express a mass density.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -826,18 +826,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>photometry [ncit]</t>
+          <t>count [ncit]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Measurement of the properties of light, especially luminous intensity.</t>
+          <t>Determining the number or amount of something.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -845,18 +845,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>spectrum [ncit]</t>
+          <t>operator [ncit]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>An array of entities, such as light waves or particles, ordered in accordance with the magnitudes of a common physical property, such as wavelength or mass.</t>
+          <t>A person that operates some apparatus or machine.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -864,18 +864,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>temperature [ncit]</t>
+          <t>peak [ncit]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A measure of the average kinetic energy of a system of particles. Temperature may be quantified, in the context of thermodynamics, as the potential of one system to transfer thermal energy to another system until both systems reach a state of thermal equilibrium.</t>
+          <t>The most extreme possible amount or value; the highest point.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -883,18 +883,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>group [ncit]</t>
+          <t>mixing [ncit]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>chemical entity</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Any number of entities (members) considered as a unit.</t>
+          <t>To bring or combine together or with something else; add as an additional element or part.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -902,18 +902,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cost [ncit]</t>
+          <t>mass density [ncit]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>The amount paid, charged, or engaged to be paid, for purchasing goods, services and financial instruments.</t>
+          <t>A measure of the compactness of a substance, expressed as its mass per unit volume.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -921,18 +921,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>shape [ncit]</t>
+          <t>mixer device [ncit]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The spatial arrangement of something as distinct from its substance.</t>
+          <t>A mechanical device designed to blend materials or an electronic device designed to blend signals.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -940,18 +940,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>direct costs [ncit]</t>
+          <t>concentration [ncit]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cost [ncit]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Costs that can be identified with a particular project or program.</t>
+          <t>The quantity of a substance per unit volume or weight; a measure of the amount of substance present in a unit amount of mixture, particularly, the amount of solute dissolved in a solvent. The amounts can be expressed as moles, masses, volumes, or parts. (ncit defined)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -959,18 +959,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>function [ncit]</t>
+          <t>spectrum [ncit]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The normal action performed by a structure or device.</t>
+          <t>An array of entities, such as light waves or particles, ordered in accordance with the magnitudes of a common physical property, such as wavelength or mass.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -978,18 +978,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>correlation [ncit]</t>
+          <t>temperature [ncit]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The degree to which two or more quantities or events are associated, a statistical relation between two or more variables such that systematic changes in the value of one variable are accompanied by systematic changes in the others. The collelation can be described by mathematical functions  (often a linear function is used). It’s a common tool for describing simple relationships without making a statement about cause and effect.</t>
+          <t>A measure of the average kinetic energy of a system of particles. Temperature may be quantified, in the context of thermodynamics, as the potential of one system to transfer thermal energy to another system until both systems reach a state of thermal equilibrium.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -997,18 +997,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>correlation [ncit]</t>
+          <t>natural rubber [ncit]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>The degree to which two or more quantities or events are associated, a statistical relation between two or more variables such that systematic changes in the value of one variable are accompanied by systematic changes in the others. The collelation can be described by mathematical functions  (often a linear function is used). It’s a common tool for describing simple relationships without making a statement about cause and effect.</t>
+          <t>The natural extract of tropical rubber plants.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1016,18 +1016,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>plasticizer [ncit]</t>
+          <t>stearic acid [ncit]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>pure substance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A substance added to plastics or other materials to make or keep them soft or pliable.</t>
+          <t>A saturated long-chain fatty acid with an 18-carbon backbone. Stearic acid is found in various animal and plant fats, and is a major component of cocoa butter and shea butter.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1035,18 +1035,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>colorimetry [ncit]</t>
+          <t>direct costs [ncit]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>cost [ncit]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>An assessment used to quantify and describe the colors within the visible spectrum of light.</t>
+          <t>Costs that can be identified with a particular project or program.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>concentration [ncit]</t>
+          <t>cost [ncit]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>The quantity of a substance per unit volume or weight; a measure of the amount of substance present in a unit amount of mixture, particularly, the amount of solute dissolved in a solvent. The amounts can be expressed as moles, masses, volumes, or parts. (ncit defined)</t>
+          <t>The amount paid, charged, or engaged to be paid, for purchasing goods, services and financial instruments.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1073,18 +1073,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>unit of mass density [ncit]</t>
+          <t>zinc [ncit]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>measurement unit label</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>An indication of the type of unit of measure being used to express a mass density.</t>
+          <t>An element with atomic symbol Zn, atomic number 30, and atomic weight 65.39.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
